--- a/sub_pro_12_fifa_tm_analysis/datasets/processed_2026/caf_fifa_tm_clean_analysis.xlsx
+++ b/sub_pro_12_fifa_tm_analysis/datasets/processed_2026/caf_fifa_tm_clean_analysis.xlsx
@@ -1,21 +1,401 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R_Files\sports_data_sci\sub_pro_12_fifa_tm_analysis\datasets\processed_2026\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3652F007-509F-4293-883C-FADE904DA1BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="123">
+  <si>
+    <t>ranking</t>
+  </si>
+  <si>
+    <t>team</t>
+  </si>
+  <si>
+    <t>confederation</t>
+  </si>
+  <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>points</t>
+  </si>
+  <si>
+    <t>squad_size</t>
+  </si>
+  <si>
+    <t>o_age</t>
+  </si>
+  <si>
+    <t>most_valuable_player</t>
+  </si>
+  <si>
+    <t>team_market_value_euros_numeric</t>
+  </si>
+  <si>
+    <t>avg_player_market_value_euros_numeric</t>
+  </si>
+  <si>
+    <t>top_player_value_euros_numeric</t>
+  </si>
+  <si>
+    <t>players_playing_abroad_percent</t>
+  </si>
+  <si>
+    <t>Morocco</t>
+  </si>
+  <si>
+    <t>CAF</t>
+  </si>
+  <si>
+    <t>UNAF</t>
+  </si>
+  <si>
+    <t>Achraf Hakimi</t>
+  </si>
+  <si>
+    <t>Senegal</t>
+  </si>
+  <si>
+    <t>WAFU - Zone A</t>
+  </si>
+  <si>
+    <t>Iliman Ndiaye</t>
+  </si>
+  <si>
+    <t>Nigeria</t>
+  </si>
+  <si>
+    <t>WAFU - Zone B</t>
+  </si>
+  <si>
+    <t>Ademola Lookman</t>
+  </si>
+  <si>
+    <t>Algeria</t>
+  </si>
+  <si>
+    <t>Rayan Aït-Nouri</t>
+  </si>
+  <si>
+    <t>Egypt</t>
+  </si>
+  <si>
+    <t>Omar Marmoush</t>
+  </si>
+  <si>
+    <t>Ivory Coast</t>
+  </si>
+  <si>
+    <t>Yan Diomande</t>
+  </si>
+  <si>
+    <t>Cameroon</t>
+  </si>
+  <si>
+    <t>UNIFFAC</t>
+  </si>
+  <si>
+    <t>Bryan Mbeumo</t>
+  </si>
+  <si>
+    <t>Tunisia</t>
+  </si>
+  <si>
+    <t>Louey Ben Farhat</t>
+  </si>
+  <si>
+    <t>Democratic Republic of the Congo</t>
+  </si>
+  <si>
+    <t>Yoane Wissa</t>
+  </si>
+  <si>
+    <t>Mali</t>
+  </si>
+  <si>
+    <t>Dorgeles Nene</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
+    <t>COSAFA</t>
+  </si>
+  <si>
+    <t>Lyle Foster</t>
+  </si>
+  <si>
+    <t>Burkina Faso</t>
+  </si>
+  <si>
+    <t>Edmond Tapsoba</t>
+  </si>
+  <si>
+    <t>Cape Verde</t>
+  </si>
+  <si>
+    <t>Wagner Pina</t>
+  </si>
+  <si>
+    <t>Ghana</t>
+  </si>
+  <si>
+    <t>Antoine Semenyo</t>
+  </si>
+  <si>
+    <t>Guinea</t>
+  </si>
+  <si>
+    <t>Serhou Guirassy</t>
+  </si>
+  <si>
+    <t>Gabon</t>
+  </si>
+  <si>
+    <t>Denis Bouanga</t>
+  </si>
+  <si>
+    <t>Uganda</t>
+  </si>
+  <si>
+    <t>CECAFA</t>
+  </si>
+  <si>
+    <t>Baba Alhassan</t>
+  </si>
+  <si>
+    <t>Angola</t>
+  </si>
+  <si>
+    <t>David Carmo</t>
+  </si>
+  <si>
+    <t>Zambia</t>
+  </si>
+  <si>
+    <t>Patson Daka</t>
+  </si>
+  <si>
+    <t>Benin</t>
+  </si>
+  <si>
+    <t>Junior Olaitan</t>
+  </si>
+  <si>
+    <t>Mozambique</t>
+  </si>
+  <si>
+    <t>Geny Catamo</t>
+  </si>
+  <si>
+    <t>Madagascar</t>
+  </si>
+  <si>
+    <t>Andy Pelmard</t>
+  </si>
+  <si>
+    <t>Comoros</t>
+  </si>
+  <si>
+    <t>Warmed Omari</t>
+  </si>
+  <si>
+    <t>Equatorial Guinea</t>
+  </si>
+  <si>
+    <t>Saul Coco</t>
+  </si>
+  <si>
+    <t>Tanzania</t>
+  </si>
+  <si>
+    <t>Novatus Miroshi</t>
+  </si>
+  <si>
+    <t>Niger</t>
+  </si>
+  <si>
+    <t>Oumar Soko</t>
+  </si>
+  <si>
+    <t>Libya</t>
+  </si>
+  <si>
+    <t>Moatasem Al-Musrati</t>
+  </si>
+  <si>
+    <t>Kenya</t>
+  </si>
+  <si>
+    <t>Michael Olunga</t>
+  </si>
+  <si>
+    <t>Mauritania</t>
+  </si>
+  <si>
+    <t>Djeidi Gasssama</t>
+  </si>
+  <si>
+    <t>The Gambia</t>
+  </si>
+  <si>
+    <t>Yankuba Minteh</t>
+  </si>
+  <si>
+    <t>Sudan</t>
+  </si>
+  <si>
+    <t>Mo Eisa</t>
+  </si>
+  <si>
+    <t>Namibia</t>
+  </si>
+  <si>
+    <t>Peter Shalulile</t>
+  </si>
+  <si>
+    <t>Sierra Leone</t>
+  </si>
+  <si>
+    <t>Juma Bah</t>
+  </si>
+  <si>
+    <t>Togo</t>
+  </si>
+  <si>
+    <t>Kevin Denkey</t>
+  </si>
+  <si>
+    <t>Malawi</t>
+  </si>
+  <si>
+    <t>Charles Petro</t>
+  </si>
+  <si>
+    <t>Rwanda</t>
+  </si>
+  <si>
+    <t>Hakim Sahabo</t>
+  </si>
+  <si>
+    <t>Zimbabwe</t>
+  </si>
+  <si>
+    <t>Munashe Garananga</t>
+  </si>
+  <si>
+    <t>Guinea-Bissau</t>
+  </si>
+  <si>
+    <t>Beto</t>
+  </si>
+  <si>
+    <t>Republic of the Congo</t>
+  </si>
+  <si>
+    <t>Christ Makosso</t>
+  </si>
+  <si>
+    <t>Central African Republic</t>
+  </si>
+  <si>
+    <t>Goduine Koyalipou</t>
+  </si>
+  <si>
+    <t>Liberia</t>
+  </si>
+  <si>
+    <t>Oscar</t>
+  </si>
+  <si>
+    <t>Lesotho</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Botswana</t>
+  </si>
+  <si>
+    <t>Thatayaone Ditlhokwe</t>
+  </si>
+  <si>
+    <t>Burundi</t>
+  </si>
+  <si>
+    <t>Youssouf Ndayishimiye</t>
+  </si>
+  <si>
+    <t>Ethiopia</t>
+  </si>
+  <si>
+    <t>Yared Baye</t>
+  </si>
+  <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
+    <t>Justice Figuareido</t>
+  </si>
+  <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
+    <t>Joseph Dhata</t>
+  </si>
+  <si>
+    <t>Mauritius</t>
+  </si>
+  <si>
+    <t>Chad</t>
+  </si>
+  <si>
+    <t>Marius Mouandilmadji</t>
+  </si>
+  <si>
+    <t>São Tomé and Príncipe</t>
+  </si>
+  <si>
+    <t>Ronaldo Lumungo</t>
+  </si>
+  <si>
+    <t>Djibouti</t>
+  </si>
+  <si>
+    <t>Somalia</t>
+  </si>
+  <si>
+    <t>Abdulsamed Abdullahi</t>
+  </si>
+  <si>
+    <t>Seychelles</t>
+  </si>
+  <si>
+    <t>Warren Mellie</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -55,7 +435,7 @@
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -63,13 +443,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +495,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +529,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +564,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,90 +740,74 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L54"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="28.54296875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ranking</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>team</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>confederation</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>squad_size</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>o_age</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>most_valuable_player</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>team_market_value_euros_numeric</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>avg_player_market_value_euros_numeric</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>top_player_value_euros_numeric</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>players_playing_abroad_percent</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>8</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>UNAF</t>
-        </is>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
       </c>
       <c r="E2">
         <v>1737</v>
@@ -444,10 +818,8 @@
       <c r="G2">
         <v>25.3</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Achraf Hakimi</t>
-        </is>
+      <c r="H2" t="s">
+        <v>15</v>
       </c>
       <c r="I2">
         <v>431750000</v>
@@ -462,24 +834,18 @@
         <v>89.7</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>12</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>WAFU - Zone A</t>
-        </is>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
       </c>
       <c r="E3">
         <v>1707</v>
@@ -490,10 +856,8 @@
       <c r="G3">
         <v>26.8</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Iliman Ndiaye</t>
-        </is>
+      <c r="H3" t="s">
+        <v>18</v>
       </c>
       <c r="I3">
         <v>456800000</v>
@@ -508,24 +872,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>26</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>WAFU - Zone B</t>
-        </is>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
       </c>
       <c r="E4">
         <v>1582</v>
@@ -536,10 +894,8 @@
       <c r="G4">
         <v>27.6</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Ademola Lookman</t>
-        </is>
+      <c r="H4" t="s">
+        <v>21</v>
       </c>
       <c r="I4">
         <v>230080000</v>
@@ -554,24 +910,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>28</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>UNAF</t>
-        </is>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
       </c>
       <c r="E5">
         <v>1561</v>
@@ -582,10 +932,8 @@
       <c r="G5">
         <v>25.8</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Rayan Aït-Nouri</t>
-        </is>
+      <c r="H5" t="s">
+        <v>23</v>
       </c>
       <c r="I5">
         <v>227750000</v>
@@ -600,24 +948,18 @@
         <v>92.3</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>31</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>UNAF</t>
-        </is>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
       </c>
       <c r="E6">
         <v>1557</v>
@@ -628,10 +970,8 @@
       <c r="G6">
         <v>28.9</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Omar Marmoush</t>
-        </is>
+      <c r="H6" t="s">
+        <v>25</v>
       </c>
       <c r="I6">
         <v>108000000</v>
@@ -646,24 +986,18 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>37</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ivory Coast</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>WAFU - Zone B</t>
-        </is>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
       </c>
       <c r="E7">
         <v>1522</v>
@@ -674,10 +1008,8 @@
       <c r="G7">
         <v>25.3</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Yan Diomande</t>
-        </is>
+      <c r="H7" t="s">
+        <v>27</v>
       </c>
       <c r="I7">
         <v>444900000</v>
@@ -692,24 +1024,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>45</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>UNIFFAC</t>
-        </is>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
       </c>
       <c r="E8">
         <v>1482</v>
@@ -720,16 +1046,14 @@
       <c r="G8">
         <v>23.8</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Bryan Mbeumo</t>
-        </is>
+      <c r="H8" t="s">
+        <v>30</v>
       </c>
       <c r="I8">
         <v>184450000</v>
       </c>
       <c r="J8">
-        <v>8380000.000000001</v>
+        <v>8380000.0000000009</v>
       </c>
       <c r="K8">
         <v>80000000</v>
@@ -738,24 +1062,18 @@
         <v>91.7</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>47</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>UNAF</t>
-        </is>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
       </c>
       <c r="E9">
         <v>1479</v>
@@ -766,10 +1084,8 @@
       <c r="G9">
         <v>25.6</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Louey Ben Farhat</t>
-        </is>
+      <c r="H9" t="s">
+        <v>32</v>
       </c>
       <c r="I9">
         <v>50600000</v>
@@ -784,24 +1100,18 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>48</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>UNIFFAC</t>
-        </is>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
       </c>
       <c r="E10">
         <v>1468</v>
@@ -812,10 +1122,8 @@
       <c r="G10">
         <v>28.3</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Yoane Wissa</t>
-        </is>
+      <c r="H10" t="s">
+        <v>34</v>
       </c>
       <c r="I10">
         <v>154900000</v>
@@ -830,24 +1138,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>54</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Mali</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>WAFU - Zone A</t>
-        </is>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
       </c>
       <c r="E11">
         <v>1458</v>
@@ -858,10 +1160,8 @@
       <c r="G11">
         <v>26.5</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Dorgeles Nene</t>
-        </is>
+      <c r="H11" t="s">
+        <v>36</v>
       </c>
       <c r="I11">
         <v>140050000</v>
@@ -876,24 +1176,18 @@
         <v>95.8</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>60</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>COSAFA</t>
-        </is>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>38</v>
       </c>
       <c r="E12">
         <v>1433</v>
@@ -904,10 +1198,8 @@
       <c r="G12">
         <v>26.8</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Lyle Foster</t>
-        </is>
+      <c r="H12" t="s">
+        <v>39</v>
       </c>
       <c r="I12">
         <v>41150000</v>
@@ -922,24 +1214,18 @@
         <v>30.4</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>62</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Burkina Faso</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>WAFU - Zone B</t>
-        </is>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
       </c>
       <c r="E13">
         <v>1413</v>
@@ -950,10 +1236,8 @@
       <c r="G13">
         <v>24.9</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Edmond Tapsoba</t>
-        </is>
+      <c r="H13" t="s">
+        <v>41</v>
       </c>
       <c r="I13">
         <v>115130000</v>
@@ -968,24 +1252,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>67</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Cape Verde</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>WAFU - Zone A</t>
-        </is>
+      <c r="B14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
       </c>
       <c r="E14">
         <v>1370</v>
@@ -996,10 +1274,8 @@
       <c r="G14">
         <v>28.4</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Wagner Pina</t>
-        </is>
+      <c r="H14" t="s">
+        <v>43</v>
       </c>
       <c r="I14">
         <v>45150000</v>
@@ -1014,24 +1290,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>72</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>WAFU - Zone B</t>
-        </is>
+      <c r="B15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
       </c>
       <c r="E15">
         <v>1351</v>
@@ -1042,16 +1312,14 @@
       <c r="G15">
         <v>26.9</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Antoine Semenyo</t>
-        </is>
+      <c r="H15" t="s">
+        <v>45</v>
       </c>
       <c r="I15">
         <v>211280000</v>
       </c>
       <c r="J15">
-        <v>8130000.000000001</v>
+        <v>8130000.0000000009</v>
       </c>
       <c r="K15">
         <v>75000000</v>
@@ -1060,24 +1328,18 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>80</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Guinea</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>WAFU - Zone A</t>
-        </is>
+      <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>17</v>
       </c>
       <c r="E16">
         <v>1307</v>
@@ -1088,10 +1350,8 @@
       <c r="G16">
         <v>25</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Serhou Guirassy</t>
-        </is>
+      <c r="H16" t="s">
+        <v>47</v>
       </c>
       <c r="I16">
         <v>72300000</v>
@@ -1106,24 +1366,18 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>86</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Gabon</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>UNIFFAC</t>
-        </is>
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s">
+        <v>29</v>
       </c>
       <c r="E17">
         <v>1276</v>
@@ -1134,10 +1388,8 @@
       <c r="G17">
         <v>28.3</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Denis Bouanga</t>
-        </is>
+      <c r="H17" t="s">
+        <v>49</v>
       </c>
       <c r="I17">
         <v>29830000</v>
@@ -1152,24 +1404,18 @@
         <v>88.2</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>88</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>CECAFA</t>
-        </is>
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s">
+        <v>51</v>
       </c>
       <c r="E18">
         <v>1264</v>
@@ -1180,10 +1426,8 @@
       <c r="G18">
         <v>27.9</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Baba Alhassan</t>
-        </is>
+      <c r="H18" t="s">
+        <v>52</v>
       </c>
       <c r="I18">
         <v>8630000</v>
@@ -1195,27 +1439,21 @@
         <v>900000</v>
       </c>
       <c r="L18">
-        <v>82.09999999999999</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>82.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>89</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>COSAFA</t>
-        </is>
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
+        <v>38</v>
       </c>
       <c r="E19">
         <v>1263</v>
@@ -1226,10 +1464,8 @@
       <c r="G19">
         <v>29.2</v>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>David Carmo</t>
-        </is>
+      <c r="H19" t="s">
+        <v>54</v>
       </c>
       <c r="I19">
         <v>52700000</v>
@@ -1241,27 +1477,21 @@
         <v>8000000</v>
       </c>
       <c r="L19">
-        <v>88.90000000000001</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>88.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>91</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>COSAFA</t>
-        </is>
+      <c r="B20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>38</v>
       </c>
       <c r="E20">
         <v>1257</v>
@@ -1272,10 +1502,8 @@
       <c r="G20">
         <v>26.1</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Patson Daka</t>
-        </is>
+      <c r="H20" t="s">
+        <v>56</v>
       </c>
       <c r="I20">
         <v>12900000</v>
@@ -1287,27 +1515,21 @@
         <v>12000000</v>
       </c>
       <c r="L20">
-        <v>34.8</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>34.799999999999997</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>92</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Benin</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>WAFU - Zone B</t>
-        </is>
+      <c r="B21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s">
+        <v>20</v>
       </c>
       <c r="E21">
         <v>1250</v>
@@ -1318,10 +1540,8 @@
       <c r="G21">
         <v>26.1</v>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Junior Olaitan</t>
-        </is>
+      <c r="H21" t="s">
+        <v>58</v>
       </c>
       <c r="I21">
         <v>16900000</v>
@@ -1336,24 +1556,18 @@
         <v>91.7</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>101</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Mozambique</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>COSAFA</t>
-        </is>
+      <c r="B22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s">
+        <v>38</v>
       </c>
       <c r="E22">
         <v>1224</v>
@@ -1364,10 +1578,8 @@
       <c r="G22">
         <v>29.1</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Geny Catamo</t>
-        </is>
+      <c r="H22" t="s">
+        <v>60</v>
       </c>
       <c r="I22">
         <v>30050000</v>
@@ -1382,24 +1594,18 @@
         <v>64.3</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>104</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Madagascar</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>COSAFA</t>
-        </is>
+      <c r="B23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s">
+        <v>38</v>
       </c>
       <c r="E23">
         <v>1199</v>
@@ -1410,10 +1616,8 @@
       <c r="G23">
         <v>27.7</v>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Andy Pelmard</t>
-        </is>
+      <c r="H23" t="s">
+        <v>62</v>
       </c>
       <c r="I23">
         <v>8180000</v>
@@ -1428,24 +1632,18 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>106</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Comoros</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>COSAFA</t>
-        </is>
+      <c r="B24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" t="s">
+        <v>38</v>
       </c>
       <c r="E24">
         <v>1193</v>
@@ -1456,10 +1654,8 @@
       <c r="G24">
         <v>24.5</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Warmed Omari</t>
-        </is>
+      <c r="H24" t="s">
+        <v>64</v>
       </c>
       <c r="I24">
         <v>12530000</v>
@@ -1474,24 +1670,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>107</v>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Equatorial Guinea</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>UNIFFAC</t>
-        </is>
+      <c r="B25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" t="s">
+        <v>29</v>
       </c>
       <c r="E25">
         <v>1190</v>
@@ -1502,10 +1692,8 @@
       <c r="G25">
         <v>25.9</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Saul Coco</t>
-        </is>
+      <c r="H25" t="s">
+        <v>66</v>
       </c>
       <c r="I25">
         <v>11680000</v>
@@ -1520,24 +1708,18 @@
         <v>89.5</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>110</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>CECAFA</t>
-        </is>
+      <c r="B26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" t="s">
+        <v>51</v>
       </c>
       <c r="E26">
         <v>1186</v>
@@ -1548,10 +1730,8 @@
       <c r="G26">
         <v>26.3</v>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Novatus Miroshi</t>
-        </is>
+      <c r="H26" t="s">
+        <v>68</v>
       </c>
       <c r="I26">
         <v>7350000</v>
@@ -1566,24 +1746,18 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>111</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Niger</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>WAFU - Zone B</t>
-        </is>
+      <c r="B27" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" t="s">
+        <v>20</v>
       </c>
       <c r="E27">
         <v>1185</v>
@@ -1594,10 +1768,8 @@
       <c r="G27">
         <v>26.2</v>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Oumar Soko</t>
-        </is>
+      <c r="H27" t="s">
+        <v>70</v>
       </c>
       <c r="I27">
         <v>10050000</v>
@@ -1612,24 +1784,18 @@
         <v>78.3</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>112</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Libya</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>UNAF</t>
-        </is>
+      <c r="B28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" t="s">
+        <v>14</v>
       </c>
       <c r="E28">
         <v>1183</v>
@@ -1640,10 +1806,8 @@
       <c r="G28">
         <v>26.4</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Moatasem Al-Musrati</t>
-        </is>
+      <c r="H28" t="s">
+        <v>72</v>
       </c>
       <c r="I28">
         <v>10730000</v>
@@ -1658,24 +1822,18 @@
         <v>31.6</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>113</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>CECAFA</t>
-        </is>
+      <c r="B29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s">
+        <v>51</v>
       </c>
       <c r="E29">
         <v>1180</v>
@@ -1686,10 +1844,8 @@
       <c r="G29">
         <v>25.8</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Michael Olunga</t>
-        </is>
+      <c r="H29" t="s">
+        <v>74</v>
       </c>
       <c r="I29">
         <v>11780000</v>
@@ -1701,27 +1857,21 @@
         <v>6000000</v>
       </c>
       <c r="L29">
-        <v>69.59999999999999</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>69.599999999999994</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>115</v>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Mauritania</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>UNAF</t>
-        </is>
+      <c r="B30" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s">
+        <v>14</v>
       </c>
       <c r="E30">
         <v>1171</v>
@@ -1732,10 +1882,8 @@
       <c r="G30">
         <v>26.5</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Djeidi Gasssama</t>
-        </is>
+      <c r="H30" t="s">
+        <v>76</v>
       </c>
       <c r="I30">
         <v>24430000</v>
@@ -1750,24 +1898,18 @@
         <v>88.5</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>116</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>The Gambia</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>WAFU - Zone A</t>
-        </is>
+      <c r="B31" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" t="s">
+        <v>17</v>
       </c>
       <c r="E31">
         <v>1162</v>
@@ -1778,10 +1920,8 @@
       <c r="G31">
         <v>25.2</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Yankuba Minteh</t>
-        </is>
+      <c r="H31" t="s">
+        <v>78</v>
       </c>
       <c r="I31">
         <v>72280000</v>
@@ -1796,24 +1936,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>117</v>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Sudan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>CECAFA</t>
-        </is>
+      <c r="B32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" t="s">
+        <v>51</v>
       </c>
       <c r="E32">
         <v>1157</v>
@@ -1824,10 +1958,8 @@
       <c r="G32">
         <v>29.1</v>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Mo Eisa</t>
-        </is>
+      <c r="H32" t="s">
+        <v>80</v>
       </c>
       <c r="I32">
         <v>3300000</v>
@@ -1842,24 +1974,18 @@
         <v>44.4</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>118</v>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Namibia</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>COSAFA</t>
-        </is>
+      <c r="B33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" t="s">
+        <v>38</v>
       </c>
       <c r="E33">
         <v>1153</v>
@@ -1870,10 +1996,8 @@
       <c r="G33">
         <v>29</v>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Peter Shalulile</t>
-        </is>
+      <c r="H33" t="s">
+        <v>82</v>
       </c>
       <c r="I33">
         <v>4250000</v>
@@ -1888,24 +2012,18 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>120</v>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Sierra Leone</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>WAFU - Zone A</t>
-        </is>
+      <c r="B34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s">
+        <v>17</v>
       </c>
       <c r="E34">
         <v>1149</v>
@@ -1916,10 +2034,8 @@
       <c r="G34">
         <v>25.3</v>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Juma Bah</t>
-        </is>
+      <c r="H34" t="s">
+        <v>84</v>
       </c>
       <c r="I34">
         <v>10500000</v>
@@ -1934,24 +2050,18 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>124</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Togo</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>WAFU - Zone B</t>
-        </is>
+      <c r="B35" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" t="s">
+        <v>20</v>
       </c>
       <c r="E35">
         <v>1140</v>
@@ -1962,10 +2072,8 @@
       <c r="G35">
         <v>25.4</v>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kevin Denkey</t>
-        </is>
+      <c r="H35" t="s">
+        <v>86</v>
       </c>
       <c r="I35">
         <v>29750000</v>
@@ -1980,24 +2088,18 @@
         <v>96</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>126</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>COSAFA</t>
-        </is>
+      <c r="B36" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s">
+        <v>38</v>
       </c>
       <c r="E36">
         <v>1134</v>
@@ -2008,10 +2110,8 @@
       <c r="G36">
         <v>26.7</v>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Charles Petro</t>
-        </is>
+      <c r="H36" t="s">
+        <v>88</v>
       </c>
       <c r="I36">
         <v>2000000</v>
@@ -2026,24 +2126,18 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>130</v>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Rwanda</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>CECAFA</t>
-        </is>
+      <c r="B37" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" t="s">
+        <v>51</v>
       </c>
       <c r="E37">
         <v>1118</v>
@@ -2054,10 +2148,8 @@
       <c r="G37">
         <v>27.2</v>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Hakim Sahabo</t>
-        </is>
+      <c r="H37" t="s">
+        <v>90</v>
       </c>
       <c r="I37">
         <v>5380000</v>
@@ -2072,24 +2164,18 @@
         <v>62.1</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>132</v>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>COSAFA</t>
-        </is>
+      <c r="B38" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" t="s">
+        <v>38</v>
       </c>
       <c r="E38">
         <v>1114</v>
@@ -2100,10 +2186,8 @@
       <c r="G38">
         <v>26.5</v>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Munashe Garananga</t>
-        </is>
+      <c r="H38" t="s">
+        <v>92</v>
       </c>
       <c r="I38">
         <v>7600000</v>
@@ -2118,24 +2202,18 @@
         <v>78.3</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>133</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Guinea-Bissau</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>WAFU - Zone A</t>
-        </is>
+      <c r="B39" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" t="s">
+        <v>17</v>
       </c>
       <c r="E39">
         <v>1108</v>
@@ -2146,10 +2224,8 @@
       <c r="G39">
         <v>26.3</v>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Beto</t>
-        </is>
+      <c r="H39" t="s">
+        <v>94</v>
       </c>
       <c r="I39">
         <v>41250000</v>
@@ -2164,24 +2240,18 @@
         <v>95.7</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>134</v>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>UNIFFAC</t>
-        </is>
+      <c r="B40" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" t="s">
+        <v>29</v>
       </c>
       <c r="E40">
         <v>1106</v>
@@ -2192,10 +2262,8 @@
       <c r="G40">
         <v>24.6</v>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Christ Makosso</t>
-        </is>
+      <c r="H40" t="s">
+        <v>96</v>
       </c>
       <c r="I40">
         <v>2330000</v>
@@ -2210,24 +2278,18 @@
         <v>60.9</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>138</v>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Central African Republic</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>UNIFFAC</t>
-        </is>
+      <c r="B41" t="s">
+        <v>97</v>
+      </c>
+      <c r="C41" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" t="s">
+        <v>29</v>
       </c>
       <c r="E41">
         <v>1084</v>
@@ -2238,10 +2300,8 @@
       <c r="G41">
         <v>25.7</v>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Goduine Koyalipou</t>
-        </is>
+      <c r="H41" t="s">
+        <v>98</v>
       </c>
       <c r="I41">
         <v>7000000</v>
@@ -2256,24 +2316,18 @@
         <v>80.8</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>140</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Liberia</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>WAFU - Zone A</t>
-        </is>
+      <c r="B42" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" t="s">
+        <v>17</v>
       </c>
       <c r="E42">
         <v>1081</v>
@@ -2284,10 +2338,8 @@
       <c r="G42">
         <v>24.3</v>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Oscar</t>
-        </is>
+      <c r="H42" t="s">
+        <v>100</v>
       </c>
       <c r="I42">
         <v>15850000</v>
@@ -2299,27 +2351,21 @@
         <v>7000000</v>
       </c>
       <c r="L42">
-        <v>73.09999999999999</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>73.099999999999994</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>143</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Lesotho</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>COSAFA</t>
-        </is>
+      <c r="B43" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" t="s">
+        <v>38</v>
       </c>
       <c r="E43">
         <v>1066</v>
@@ -2330,10 +2376,8 @@
       <c r="G43">
         <v>28.1</v>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="H43" t="s">
+        <v>102</v>
       </c>
       <c r="I43">
         <v>675000</v>
@@ -2345,24 +2389,18 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>144</v>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Botswana</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>COSAFA</t>
-        </is>
+      <c r="B44" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" t="s">
+        <v>38</v>
       </c>
       <c r="E44">
         <v>1062</v>
@@ -2373,10 +2411,8 @@
       <c r="G44">
         <v>29.9</v>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Thatayaone Ditlhokwe</t>
-        </is>
+      <c r="H44" t="s">
+        <v>104</v>
       </c>
       <c r="I44">
         <v>3080000</v>
@@ -2391,24 +2427,18 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>145</v>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Burundi</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>CECAFA</t>
-        </is>
+      <c r="B45" t="s">
+        <v>105</v>
+      </c>
+      <c r="C45" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" t="s">
+        <v>51</v>
       </c>
       <c r="E45">
         <v>1060</v>
@@ -2419,10 +2449,8 @@
       <c r="G45">
         <v>27.2</v>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Youssouf Ndayishimiye</t>
-        </is>
+      <c r="H45" t="s">
+        <v>106</v>
       </c>
       <c r="I45">
         <v>12180000</v>
@@ -2437,24 +2465,18 @@
         <v>79.2</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>147</v>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Ethiopia</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>CECAFA</t>
-        </is>
+      <c r="B46" t="s">
+        <v>107</v>
+      </c>
+      <c r="C46" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" t="s">
+        <v>51</v>
       </c>
       <c r="E46">
         <v>1055</v>
@@ -2465,10 +2487,8 @@
       <c r="G46">
         <v>27.4</v>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Yared Baye</t>
-        </is>
+      <c r="H46" t="s">
+        <v>108</v>
       </c>
       <c r="I46">
         <v>2780000</v>
@@ -2480,27 +2500,21 @@
         <v>250000</v>
       </c>
       <c r="L46">
-        <v>8.699999999999999</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>159</v>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Eswatini</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>COSAFA</t>
-        </is>
+      <c r="B47" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" t="s">
+        <v>38</v>
       </c>
       <c r="E47">
         <v>1011</v>
@@ -2511,10 +2525,8 @@
       <c r="G47">
         <v>27.8</v>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Justice Figuareido</t>
-        </is>
+      <c r="H47" t="s">
+        <v>110</v>
       </c>
       <c r="I47">
         <v>1080000</v>
@@ -2529,24 +2541,18 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>168</v>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>South Sudan</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>CECAFA</t>
-        </is>
+      <c r="B48" t="s">
+        <v>111</v>
+      </c>
+      <c r="C48" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" t="s">
+        <v>51</v>
       </c>
       <c r="E48">
         <v>978</v>
@@ -2557,10 +2563,8 @@
       <c r="G48">
         <v>25.1</v>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Joseph Dhata</t>
-        </is>
+      <c r="H48" t="s">
+        <v>112</v>
       </c>
       <c r="I48">
         <v>1600000</v>
@@ -2575,24 +2579,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>176</v>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Mauritius</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>COSAFA</t>
-        </is>
+      <c r="B49" t="s">
+        <v>113</v>
+      </c>
+      <c r="C49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" t="s">
+        <v>38</v>
       </c>
       <c r="E49">
         <v>916</v>
@@ -2603,10 +2601,8 @@
       <c r="G49">
         <v>28.1</v>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="H49" t="s">
+        <v>102</v>
       </c>
       <c r="I49">
         <v>900000</v>
@@ -2618,24 +2614,18 @@
         <v>65.2</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>177</v>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Chad</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>UNIFFAC</t>
-        </is>
+      <c r="B50" t="s">
+        <v>114</v>
+      </c>
+      <c r="C50" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" t="s">
+        <v>29</v>
       </c>
       <c r="E50">
         <v>915</v>
@@ -2646,10 +2636,8 @@
       <c r="G50">
         <v>26.2</v>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Marius Mouandilmadji</t>
-        </is>
+      <c r="H50" t="s">
+        <v>115</v>
       </c>
       <c r="I50">
         <v>4730000</v>
@@ -2664,24 +2652,18 @@
         <v>77.3</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>189</v>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>São Tomé and Príncipe</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>UNIFFAC</t>
-        </is>
+      <c r="B51" t="s">
+        <v>116</v>
+      </c>
+      <c r="C51" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" t="s">
+        <v>29</v>
       </c>
       <c r="E51">
         <v>872</v>
@@ -2692,10 +2674,8 @@
       <c r="G51">
         <v>25.5</v>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Ronaldo Lumungo</t>
-        </is>
+      <c r="H51" t="s">
+        <v>117</v>
       </c>
       <c r="I51">
         <v>1430000</v>
@@ -2710,24 +2690,18 @@
         <v>91.7</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>196</v>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Djibouti</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>CECAFA</t>
-        </is>
+      <c r="B52" t="s">
+        <v>118</v>
+      </c>
+      <c r="C52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" t="s">
+        <v>51</v>
       </c>
       <c r="E52">
         <v>847</v>
@@ -2738,10 +2712,8 @@
       <c r="G52">
         <v>26.1</v>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="H52" t="s">
+        <v>102</v>
       </c>
       <c r="I52">
         <v>575000</v>
@@ -2753,24 +2725,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>200</v>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Somalia</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>CECAFA</t>
-        </is>
+      <c r="B53" t="s">
+        <v>119</v>
+      </c>
+      <c r="C53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" t="s">
+        <v>51</v>
       </c>
       <c r="E53">
         <v>829</v>
@@ -2781,10 +2747,8 @@
       <c r="G53">
         <v>25.5</v>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Abdulsamed Abdullahi</t>
-        </is>
+      <c r="H53" t="s">
+        <v>120</v>
       </c>
       <c r="I53">
         <v>1840000</v>
@@ -2799,24 +2763,18 @@
         <v>63.2</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>203</v>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Seychelles</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>CAF</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>COSAFA</t>
-        </is>
+      <c r="B54" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" t="s">
+        <v>38</v>
       </c>
       <c r="E54">
         <v>805</v>
@@ -2827,10 +2785,8 @@
       <c r="G54">
         <v>24.9</v>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Warren Mellie</t>
-        </is>
+      <c r="H54" t="s">
+        <v>122</v>
       </c>
       <c r="I54">
         <v>1030000</v>
@@ -2842,7 +2798,7 @@
         <v>125000</v>
       </c>
       <c r="L54">
-        <v>17.4</v>
+        <v>17.399999999999999</v>
       </c>
     </row>
   </sheetData>
